--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -423,11 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF31"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,12 +601,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>videos/dummy-q01.mp4</t>
+          <t>videos/q01.mp4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>繁殖・分娩</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -616,27 +617,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>【仮問題1】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画の人は、豚舎に入る前に何をしていますか？</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>長靴をはきかえている</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>手を洗っている</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>豚にえさをやっている</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>服を着がえている</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -644,44 +645,84 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>【仮】解説1。本物の動画ができたらここに根拠を書く。</t>
+          <t>豚舎の入口で、外で使う長靴と豚舎の中で使う長靴を分けています。外の汚れ（病気のもと）を豚舎に持ち込まないためです。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Placeholder 1] Which action in the video is NOT correct?</t>
+          <t>What is the person in the video doing before entering the pig house?</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>Changing boots</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>Washing hands</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>Feeding the pigs</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>Changing clothes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Người trong video làm gì trước khi vào chuồng heo?</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Thay ủng</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Rửa tay</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Cho heo ăn</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Thay quần áo</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan orang dalam video sebelum masuk kandang babi?</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Mengganti sepatu bot</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Mencuci tangan</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Memberi makan babi</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mengganti pakaian</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -696,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>videos/dummy-q02.mp4</t>
+          <t>videos/q02.mp4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>子豚・育成</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -712,72 +753,112 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>【仮問題2】動画の豚に見られる異常はどれですか？</t>
+          <t>動画の人は、作業の前に何を着けていますか？</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>使い捨て手袋</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>マスク</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>ヘルメット</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>エプロン</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>【仮】解説2。本物の動画ができたらここに根拠を書く。</t>
+          <t>注射などの作業の前に使い捨て手袋を着けます。手の汚れを薬や豚につけないため、また薬が手につかないためです。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Placeholder 2] What abnormality is seen in the pig in the video?</t>
+          <t>What is the person in the video putting on before the work?</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>Disposable gloves</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>A mask</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>A helmet</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+          <t>An apron</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Người trong video đeo gì trước khi làm việc?</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Găng tay dùng một lần</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Khẩu trang</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mũ bảo hộ</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Tạp dề</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Apa yang dipakai orang dalam video sebelum bekerja?</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Sarung tangan sekali pakai</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Masker</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Celemek</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -792,7 +873,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>videos/dummy-q03.mp4</t>
+          <t>videos/q03.mp4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,72 +889,112 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>【仮問題3】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画では何をしていますか？</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>注射器を組み立てている</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>注射器を洗っている</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>豚に注射している</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>薬を捨てている</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>【仮】解説3。本物の動画ができたらここに根拠を書く。</t>
+          <t>注射の前に注射器と針を組み立てて準備をしています。針がゆるんでいないか確認します。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Placeholder 3] In the situation shown, what should be done next?</t>
+          <t>What is being done in the video?</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>Assembling a syringe</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>Washing a syringe</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>Injecting a pig</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+          <t>Throwing away medicine</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Lắp ráp ống tiêm</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Rửa ống tiêm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tiêm cho heo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Vứt bỏ thuốc</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Apa yang sedang dilakukan dalam video?</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Merakit alat suntik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Mencuci alat suntik</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Menyuntik babi</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Membuang obat</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -888,12 +1009,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>videos/dummy-q04.mp4</t>
+          <t>videos/q04.mp4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>飼料・栄養</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -904,72 +1025,112 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>【仮問題4】動画の場面で、危険なのはどれですか？</t>
+          <t>動画では何をしていますか？</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>【仮】危険A</t>
+          <t>薬のびんから注射器に薬を吸っている</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>【仮】危険B</t>
+          <t>薬を豚に飲ませている</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>【仮】危険C</t>
+          <t>注射器を消毒している</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>【仮】危険D</t>
+          <t>びんに水を入れている</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>【仮】解説4。本物の動画ができたらここに根拠を書く。</t>
+          <t>薬のびんに針をさして、注射器に薬を吸い上げています。決められた量を正確に吸います。</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Placeholder 4] What is dangerous in the situation shown?</t>
+          <t>What is being done in the video?</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[TBD] hazard A</t>
+          <t>Drawing medicine from the bottle into the syringe</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[TBD] hazard B</t>
+          <t>Giving medicine to a pig by mouth</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[TBD] hazard C</t>
+          <t>Disinfecting the syringe</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+          <t>Filling the bottle with water</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Hút thuốc từ lọ vào ống tiêm</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Cho heo uống thuốc</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Khử trùng ống tiêm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Đổ nước vào lọ</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Apa yang sedang dilakukan dalam video?</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Menyedot obat dari botol ke alat suntik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Memberi obat ke babi lewat mulut</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Mendisinfeksi alat suntik</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Mengisi botol dengan air</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
@@ -984,12 +1145,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>videos/dummy-q05.mp4</t>
+          <t>videos/q05.mp4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>飼養環境・施設</t>
+          <t>子豚・育成</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1000,27 +1161,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>【仮問題5】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画では、子豚に何をしていますか？</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>注射をして、赤いスプレーで印をつけている</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>耳に番号をつけている</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>体重をはかっている</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>えさをやっている</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1028,44 +1189,84 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>【仮】解説5。本物の動画ができたらここに根拠を書く。</t>
+          <t>子豚に注射をしたあと、赤いスプレーで印をつけています。印は「注射がすんだ」しるしです。</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[Placeholder 5] Which action in the video is NOT correct?</t>
+          <t>What is being done to the piglets in the video?</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>Injecting them and marking them with red spray</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>Putting number tags on their ears</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>Weighing them</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+          <t>Feeding them</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì với heo con?</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Tiêm rồi đánh dấu bằng sơn xịt màu đỏ</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gắn số vào tai</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Cân heo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Cho heo ăn</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan pada anak babi dalam video?</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Menyuntik lalu menandai dengan semprotan merah</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Memasang nomor di telinga</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Menimbang berat</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Memberi makan</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1080,12 +1281,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>videos/dummy-q06.mp4</t>
+          <t>videos/q06.mp4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>肉豚・出荷・肉</t>
+          <t>子豚・育成</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1096,72 +1297,112 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>【仮問題6】動画の豚に見られる異常はどれですか？</t>
+          <t>注射のあと、子豚に赤いスプレーをかけるのはなぜですか？</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>注射がすんだ豚を見分けるため</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>豚を元気にするため</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>虫をよけるため</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>きずを消毒するため</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>【仮】解説6。本物の動画ができたらここに根拠を書く。</t>
+          <t>印がないと、同じ豚に2回注射したり、注射をしていない豚を見のがしたりします。印を見て「まだの豚」だけに注射します。</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[Placeholder 6] What abnormality is seen in the pig in the video?</t>
+          <t>Why is red spray put on the piglet after the injection?</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>To tell which pigs have already been injected</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>To make the pig healthier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>To keep insects away</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+          <t>To disinfect a wound</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Vì sao xịt sơn đỏ lên heo con sau khi tiêm?</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Để phân biệt heo đã tiêm</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Để heo khỏe hơn</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Để đuổi côn trùng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Để sát trùng vết thương</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mengapa anak babi disemprot merah setelah disuntik?</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Untuk membedakan babi yang sudah disuntik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Untuk membuat babi lebih sehat</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Untuk mengusir serangga</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Untuk mendisinfeksi luka</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
@@ -1176,12 +1417,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>videos/dummy-q07.mp4</t>
+          <t>videos/q07.mp4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>経営理念・行動規範</t>
+          <t>子豚・育成</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1192,72 +1433,112 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>【仮問題7】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画の豚房で、まだ注射をしていない子豚はどれですか？</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>赤い印がない子豚</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>赤い印がある子豚</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>寝ている子豚</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>小さい子豚</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>【仮】解説7。本物の動画ができたらここに根拠を書く。</t>
+          <t>赤い印がついている豚は注射がすんでいます。印のない豚をさがして注射します。</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[Placeholder 7] In the situation shown, what should be done next?</t>
+          <t>In the pen shown, which piglets have NOT been injected yet?</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>Piglets without a red mark</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>Piglets with a red mark</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>Piglets that are sleeping</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+          <t>The smaller piglets</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Trong ô chuồng ở video, heo con nào CHƯA được tiêm?</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Heo con không có dấu đỏ</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Heo con có dấu đỏ</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heo con đang ngủ</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Heo con nhỏ</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Di kandang dalam video, anak babi mana yang BELUM disuntik?</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Anak babi tanpa tanda merah</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Anak babi dengan tanda merah</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Anak babi yang tidur</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Anak babi yang kecil</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
@@ -1272,7 +1553,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>videos/dummy-q08.mp4</t>
+          <t>videos/q08.mp4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1288,72 +1569,112 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>【仮問題8】動画の場面で、危険なのはどれですか？</t>
+          <t>動画の場所と作業はどれですか？</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>【仮】危険A</t>
+          <t>母豚の豚舎で、注射の薬を吸っている</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>【仮】危険B</t>
+          <t>子豚の豚舎で、えさを配っている</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>【仮】危険C</t>
+          <t>分娩房で、子豚を運んでいる</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>【仮】危険D</t>
+          <t>事務所で、記録を書いている</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>【仮】解説8。本物の動画ができたらここに根拠を書く。</t>
+          <t>ストール（1頭ずつの柵）に入った母豚のとなりで、小さいびん（バイアル）から注射器に薬を吸っています。</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[Placeholder 8] What is dangerous in the situation shown?</t>
+          <t>Where is the video taken, and what is being done?</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[TBD] hazard A</t>
+          <t>In the sow house, drawing medicine into a syringe</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[TBD] hazard B</t>
+          <t>In the piglet house, giving feed</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[TBD] hazard C</t>
+          <t>In a farrowing pen, carrying piglets</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+          <t>In the office, writing records</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Video quay ở đâu và đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Ở chuồng heo nái, hút thuốc vào ống tiêm</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Ở chuồng heo con, phát thức ăn</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ở ô đẻ, bế heo con</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ở văn phòng, ghi sổ</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Di mana video ini diambil dan apa yang dilakukan?</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Di kandang induk, menyedot obat ke alat suntik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Di kandang anak babi, membagi pakan</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Di kandang beranak, membawa anak babi</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Di kantor, menulis catatan</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
@@ -1368,7 +1689,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>videos/dummy-q09.mp4</t>
+          <t>videos/q09.mp4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1384,27 +1705,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>【仮問題9】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画では、子豚をどうやって注射していますか？</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>片手で子豚をおさえて、もう片方の手で注射している</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>子豚を走らせながら注射している</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>二人で子豚を持ち上げている</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>子豚をひもでしばっている</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1412,44 +1733,84 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>【仮】解説9。本物の動画ができたらここに根拠を書く。</t>
+          <t>子豚が動くと針が折れたり、ちがう場所に刺さったりします。片手でしっかりおさえて（保定して）から注射します。</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[Placeholder 9] Which action in the video is NOT correct?</t>
+          <t>How is the piglet being injected in the video?</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>Holding the piglet with one hand and injecting with the other</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>Injecting while the piglet runs</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>Two people lifting the piglet</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+          <t>Tying the piglet with a rope</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Trong video, heo con được tiêm như thế nào?</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Một tay giữ heo con, tay kia tiêm</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Tiêm khi heo con đang chạy</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hai người nhấc heo con lên</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Buộc heo con bằng dây</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bagaimana anak babi disuntik dalam video?</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Satu tangan memegang anak babi, tangan lain menyuntik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Menyuntik sambil anak babi berlari</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Dua orang mengangkat anak babi</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Mengikat anak babi dengan tali</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
@@ -1464,7 +1825,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>videos/dummy-q10.mp4</t>
+          <t>videos/q10.mp4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1480,72 +1841,112 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>【仮問題10】動画の豚に見られる異常はどれですか？</t>
+          <t>動画では何をしていますか？</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>使ったあとの注射器を分解して洗っている</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>新しい注射器を箱から出している</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>注射器に薬を入れている</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>注射器を豚に刺している</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>【仮】解説10。本物の動画ができたらここに根拠を書く。</t>
+          <t>使った注射器はそのままにせず、分解して洗い、きれいにしてから片づけます。よごれた注射器は病気を広げます。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[Placeholder 10] What abnormality is seen in the pig in the video?</t>
+          <t>What is being done in the video?</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>Taking apart and washing a used syringe</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>Taking a new syringe out of the box</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>Filling a syringe with medicine</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+          <t>Injecting a pig with the syringe</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Tháo rời và rửa ống tiêm đã dùng</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Lấy ống tiêm mới ra khỏi hộp</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bơm thuốc vào ống tiêm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Tiêm cho heo</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Apa yang sedang dilakukan dalam video?</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Membongkar dan mencuci alat suntik bekas</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Mengeluarkan alat suntik baru dari kotak</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Mengisi obat ke alat suntik</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Menyuntik babi</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -1560,12 +1961,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>videos/dummy-q11.mp4</t>
+          <t>videos/q11.mp4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>飼料・栄養</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1576,72 +1977,112 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>【仮問題11】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画の人が着ているものは何ですか？</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>使い捨ての白い防護服と長靴</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>ふだんの服と運動靴</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>雨がっぱとサンダル</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>作業ズボンだけ</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>【仮】解説11。本物の動画ができたらここに根拠を書く。</t>
+          <t>外から来た人（獣医など）は、白い使い捨ての防護服（つなぎ）と長靴を着けて豚舎に入ります。外の病気を持ち込まず、持ち出さないためです。</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Placeholder 11] In the situation shown, what should be done next?</t>
+          <t>What is the person in the video wearing?</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>A disposable white coverall and boots</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>Everyday clothes and sneakers</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>A raincoat and sandals</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+          <t>Only work trousers</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Người trong video mặc gì?</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Bộ đồ bảo hộ trắng dùng một lần và ủng</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Quần áo thường và giày thể thao</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Áo mưa và dép</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Chỉ quần lao động</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Apa yang dipakai orang dalam video?</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Baju pelindung putih sekali pakai dan sepatu bot</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Pakaian biasa dan sepatu olahraga</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Jas hujan dan sandal</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Hanya celana kerja</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
@@ -1656,12 +2097,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>videos/dummy-q12.mp4</t>
+          <t>videos/q12.mp4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>飼養環境・施設</t>
+          <t>肉豚・出荷・肉</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1672,72 +2113,112 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>【仮問題12】動画の場面で、危険なのはどれですか？</t>
+          <t>動画で豚の鼻にかけている道具は何のためですか？</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>【仮】危険A</t>
+          <t>豚が動かないようにおさえる（保定する）ため</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>【仮】危険B</t>
+          <t>豚に水を飲ませるため</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>【仮】危険C</t>
+          <t>豚の体重をはかるため</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>【仮】危険D</t>
+          <t>豚を運ぶため</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>【仮】解説12。本物の動画ができたらここに根拠を書く。</t>
+          <t>鼻にワイヤーをかける道具（鼻保定器・スネア）です。大きい豚は手ではおさえられないので、採血や注射のときに使います。</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Placeholder 12] What is dangerous in the situation shown?</t>
+          <t>What is the tool on the pig's snout in the video for?</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>[TBD] hazard A</t>
+          <t>To hold the pig still (restraint)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>[TBD] hazard B</t>
+          <t>To give the pig water</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[TBD] hazard C</t>
+          <t>To weigh the pig</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+          <t>To carry the pig</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Dụng cụ móc vào mũi heo trong video dùng để làm gì?</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Để giữ heo đứng yên (cố định)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Để cho heo uống nước</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Để cân heo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Để khiêng heo</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Untuk apa alat yang dipasang di hidung babi dalam video?</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Untuk menahan babi agar tidak bergerak</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Untuk memberi babi minum</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Untuk menimbang babi</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Untuk mengangkut babi</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
@@ -1752,12 +2233,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>videos/dummy-q13.mp4</t>
+          <t>videos/q13.mp4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>肉豚・出荷・肉</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1768,27 +2249,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>【仮問題13】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画では、豚に何をしていますか？</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>首から血をとっている（採血）</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>首に薬を注射している</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>首の温度をはかっている</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>首のきずを消毒している</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1796,44 +2277,84 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>【仮】解説13。本物の動画ができたらここに根拠を書く。</t>
+          <t>鼻保定をした豚の首から注射器で血をとっています。血は病気の検査に使います。</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Placeholder 13] Which action in the video is NOT correct?</t>
+          <t>What is being done to the pig in the video?</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>Taking blood from the neck (blood sampling)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>Injecting medicine into the neck</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>Measuring the temperature of the neck</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+          <t>Disinfecting a wound on the neck</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì với con heo?</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Lấy máu ở cổ (lấy mẫu máu)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Tiêm thuốc vào cổ</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Đo nhiệt độ ở cổ</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Sát trùng vết thương ở cổ</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan pada babi dalam video?</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Mengambil darah dari leher (pengambilan darah)</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Menyuntik obat ke leher</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Mengukur suhu leher</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Mendisinfeksi luka di leher</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
@@ -1848,12 +2369,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>videos/dummy-q14.mp4</t>
+          <t>videos/q14.mp4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>経営理念・行動規範</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1864,72 +2385,112 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>【仮問題14】動画の豚に見られる異常はどれですか？</t>
+          <t>動画で、床にならんでいるのは何ですか？このあと何をしますか？</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>死んだ子豚。原因を調べるために体を開く（解剖）</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>寝ている子豚。起こしてえさをやる</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>生まれたばかりの子豚。母豚に返す</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>病気の子豚。注射をする</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>【仮】解説14。本物の動画ができたらここに根拠を書く。</t>
+          <t>死んだ子豚をならべて、獣医が体を開いて死んだ原因を調べます（剖検）。手袋と防護服をつけて行います。</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Placeholder 14] What abnormality is seen in the pig in the video?</t>
+          <t>What is lying on the floor in the video, and what happens next?</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>Dead piglets. They will be opened to find the cause of death (necropsy)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>Sleeping piglets. They will be woken and fed</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>Newborn piglets. They will be returned to the sow</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+          <t>Sick piglets. They will be injected</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Trong video, thứ nằm trên sàn là gì và tiếp theo làm gì?</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Heo con đã chết. Sẽ mổ để tìm nguyên nhân chết (mổ khám)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Heo con đang ngủ. Sẽ đánh thức và cho ăn</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heo con mới sinh. Sẽ trả về heo mẹ</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Heo con bị bệnh. Sẽ tiêm thuốc</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Apa yang terbaring di lantai dalam video, dan apa yang dilakukan selanjutnya?</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Anak babi mati. Akan dibedah untuk mencari penyebab kematian (nekropsi)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Anak babi tidur. Akan dibangunkan dan diberi makan</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Anak babi baru lahir. Akan dikembalikan ke induk</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Anak babi sakit. Akan disuntik</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -1944,7 +2505,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>videos/dummy-q15.mp4</t>
+          <t>videos/q15.mp4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1960,72 +2521,112 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>【仮問題15】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画の豚舎はどれですか？</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>母豚が1頭ずつ柵に入っている豚舎（ストール）</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>子豚がたくさんいる離乳舎</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>出荷前の大きい豚の豚舎</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>えさを作る部屋</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>【仮】解説15。本物の動画ができたらここに根拠を書く。</t>
+          <t>母豚が1頭ずつ入る柵（ストール）がならぶ豚舎です。上に青い給餌器（えさの入れもの）があります。</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Placeholder 15] In the situation shown, what should be done next?</t>
+          <t>Which kind of pig house is shown in the video?</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>A house where sows are kept one per stall</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>A nursery with many piglets</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>A house for large pigs before shipping</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+          <t>A feed preparation room</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Chuồng trong video là loại nào?</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Chuồng heo nái nhốt từng con trong ô (chuồng cũi)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Chuồng cai sữa có nhiều heo con</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Chuồng heo lớn trước khi xuất bán</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Phòng trộn thức ăn</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kandang jenis apa yang terlihat dalam video?</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Kandang induk, satu ekor per sekat (stall)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Kandang sapih dengan banyak anak babi</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Kandang babi besar sebelum dijual</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Ruang pembuatan pakan</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
@@ -2040,7 +2641,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>videos/dummy-q16.mp4</t>
+          <t>videos/q16.mp4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2056,72 +2657,112 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>【仮問題16】動画の場面で、危険なのはどれですか？</t>
+          <t>動画の豚舎にいる豚はどれですか？</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>【仮】危険A</t>
+          <t>母豚からはなれた子豚（離乳子豚）</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>【仮】危険B</t>
+          <t>妊娠している母豚</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>【仮】危険C</t>
+          <t>出荷する大きい豚</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>【仮】危険D</t>
+          <t>生まれたばかりの子豚と母豚</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>【仮】解説16。本物の動画ができたらここに根拠を書く。</t>
+          <t>小さい子豚がたくさん入っている豚舎です。丸い給餌器があり、母豚はいません。母豚からはなれた（離乳した）子豚の豚舎です。</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Placeholder 16] What is dangerous in the situation shown?</t>
+          <t>Which pigs are in the house shown in the video?</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[TBD] hazard A</t>
+          <t>Weaned piglets (separated from the sow)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[TBD] hazard B</t>
+          <t>Pregnant sows</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[TBD] hazard C</t>
+          <t>Large pigs ready for shipping</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+          <t>Newborn piglets with their sow</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Heo trong chuồng ở video là loại nào?</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Heo con đã cai sữa (tách khỏi heo mẹ)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Heo nái đang mang thai</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Heo lớn sắp xuất bán</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Heo con mới sinh cùng heo mẹ</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Babi apa yang ada di kandang dalam video?</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Anak babi sapih (dipisah dari induk)</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Induk babi bunting</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Babi besar siap jual</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Anak babi baru lahir bersama induk</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
@@ -2136,12 +2777,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>videos/dummy-q17.mp4</t>
+          <t>videos/q17.mp4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>衛生・防疫</t>
+          <t>飼養環境・施設</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2152,27 +2793,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>【仮問題17】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画にうつっている大きなタンクは何ですか？</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>えさ（飼料）をためるタンク</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>水をためるタンク</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>ふん尿をためるタンク</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>ガスをためるタンク</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2180,44 +2821,84 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>【仮】解説17。本物の動画ができたらここに根拠を書く。</t>
+          <t>豚舎の外に立っている大きなタンクは飼料タンク（サイロ）です。トラックで運ばれたえさをためて、豚舎の中に送ります。</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Placeholder 17] Which action in the video is NOT correct?</t>
+          <t>What is the large tank shown in the video?</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>A tank that stores feed</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>A tank that stores water</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>A tank that stores manure</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+          <t>A tank that stores gas</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Bồn lớn trong video là gì?</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Bồn chứa thức ăn</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Bồn chứa nước</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bồn chứa phân</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bồn chứa gas</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tangki besar dalam video itu apa?</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Tangki penyimpan pakan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tangki penyimpan air</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Tangki penyimpan kotoran</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Tangki penyimpan gas</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
@@ -2232,12 +2913,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>videos/dummy-q18.mp4</t>
+          <t>videos/q18.mp4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>飼料・栄養</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2248,72 +2929,112 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>【仮問題18】動画の豚に見られる異常はどれですか？</t>
+          <t>動画では、どこで何をしていますか？</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>事務所で、薬のびんから注射器に薬を吸っている</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>豚舎で、豚に注射している</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>台所で、薬を水にとかしている</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>車の中で、薬を数えている</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>【仮】解説18。本物の動画ができたらここに根拠を書く。</t>
+          <t>きれいな場所（事務所）で、薬のびんに針をさして注射器に薬を吸っています。</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Placeholder 18] What abnormality is seen in the pig in the video?</t>
+          <t>Where is the video taken, and what is being done?</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>In the office, drawing medicine from a bottle into a syringe</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>In the pig house, injecting a pig</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>In a kitchen, dissolving medicine in water</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
+          <t>In a car, counting medicine</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Video quay ở đâu và đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Ở văn phòng, hút thuốc từ lọ vào ống tiêm</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Ở chuồng, tiêm cho heo</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ở bếp, hòa thuốc vào nước</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Trong xe, đếm thuốc</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Di mana video ini diambil dan apa yang dilakukan?</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Di kantor, menyedot obat dari botol ke alat suntik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Di kandang, menyuntik babi</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Di dapur, melarutkan obat dalam air</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Di dalam mobil, menghitung obat</t>
+        </is>
+      </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
@@ -2328,12 +3049,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>videos/dummy-q19.mp4</t>
+          <t>videos/q19.mp4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>飼養環境・施設</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2344,72 +3065,112 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>【仮問題19】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画は豚舎の入口です。白い長靴と汚れた長靴を分けて置くのはなぜですか？</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>外の汚れを豚舎の中に持ち込まないため</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>長靴をかわかすため</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>サイズで分けるため</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>見た目をきれいにするため</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>【仮】解説19。本物の動画ができたらここに根拠を書く。</t>
+          <t>入口で「外用」と「中用」の長靴をはきかえます。汚れた長靴で中に入ると、外の病気を豚舎に持ち込みます。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>[Placeholder 19] In the situation shown, what should be done next?</t>
+          <t>The video shows the entrance of a pig house. Why are the white boots and the dirty boots kept separately?</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>So that dirt from outside is not carried into the pig house</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>To dry the boots</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>To sort them by size</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
+          <t>To make the entrance look tidy</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Video là lối vào chuồng heo. Vì sao ủng trắng và ủng bẩn được để riêng?</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Để không mang bẩn từ bên ngoài vào chuồng</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Để phơi khô ủng</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Để phân theo cỡ</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Để trông gọn gàng</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Video menunjukkan pintu masuk kandang. Mengapa sepatu bot putih dan sepatu bot kotor dipisahkan?</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Agar kotoran dari luar tidak terbawa ke dalam kandang</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Untuk mengeringkan sepatu bot</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Untuk memisahkan menurut ukuran</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Agar terlihat rapi</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
@@ -2424,12 +3185,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>videos/dummy-q20.mp4</t>
+          <t>videos/q20.mp4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>肉豚・出荷・肉</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2440,1037 +3201,117 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>【仮問題20】動画の場面で、危険なのはどれですか？</t>
+          <t>動画の人は何をしていますか？</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>【仮】危険A</t>
+          <t>防護服を着て、豚舎の中を歩いて豚を見て回っている</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>【仮】危険B</t>
+          <t>豚舎をそうじしている</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>【仮】危険C</t>
+          <t>豚を追い出している</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>【仮】危険D</t>
+          <t>えさを配っている</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>【仮】解説20。本物の動画ができたらここに根拠を書く。</t>
+          <t>防護服と長靴を着けた人が通路を歩いて、豚のようすを見て回っています（見回り）。元気がない豚や具合の悪い豚がいないか確認します。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>[Placeholder 20] What is dangerous in the situation shown?</t>
+          <t>What is the person in the video doing?</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>[TBD] hazard A</t>
+          <t>Wearing a coverall and walking through the house to check the pigs</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[TBD] hazard B</t>
+          <t>Cleaning the pig house</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[TBD] hazard C</t>
+          <t>Driving the pigs out</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
+          <t>Giving feed</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Người trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Mặc đồ bảo hộ, đi trong chuồng để quan sát heo</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dọn dẹp chuồng</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lùa heo ra ngoài</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Phát thức ăn</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan orang dalam video?</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Memakai baju pelindung dan berjalan di kandang untuk memeriksa babi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Membersihkan kandang</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Mengusir babi keluar</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Membagikan pakan</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>q21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>videos/dummy-q21.mp4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>経営理念・行動規範</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>【仮問題21】動画の作業で、正しくないのはどれですか？</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>【仮】誤っている手順A</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順B</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順C</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順D</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>【仮】解説21。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>[Placeholder 21] Which action in the video is NOT correct?</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>[TBD] wrong step A</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[TBD] correct step B</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>[TBD] correct step C</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>q22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>videos/dummy-q22.mp4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>繁殖・分娩</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>【仮問題22】動画の豚に見られる異常はどれですか？</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>【仮】異常なし</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補B</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補C</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補D</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>【仮】解説22。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>[Placeholder 22] What abnormality is seen in the pig in the video?</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>[TBD] nothing abnormal</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>[TBD] candidate B</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>[TBD] candidate C</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>q23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>videos/dummy-q23.mp4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>子豚・育成</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>【仮問題23】動画の場面で、次にすべき行動はどれですか？</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>【仮】行動A</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>【仮】行動B</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>【仮】行動C</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>【仮】行動D</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>【仮】解説23。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>[Placeholder 23] In the situation shown, what should be done next?</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>[TBD] action A</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>[TBD] action B</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>[TBD] action C</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>q24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>videos/dummy-q24.mp4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>衛生・防疫</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>【仮問題24】動画の場面で、危険なのはどれですか？</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>【仮】危険A</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>【仮】危険B</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>【仮】危険C</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>【仮】危険D</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>【仮】解説24。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>[Placeholder 24] What is dangerous in the situation shown?</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>[TBD] hazard A</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[TBD] hazard B</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>[TBD] hazard C</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>q25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>videos/dummy-q25.mp4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>飼料・栄養</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>【仮問題25】動画の作業で、正しくないのはどれですか？</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>【仮】誤っている手順A</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順B</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順C</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順D</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>【仮】解説25。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>[Placeholder 25] Which action in the video is NOT correct?</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>[TBD] wrong step A</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[TBD] correct step B</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>[TBD] correct step C</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>q26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>videos/dummy-q26.mp4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>飼養環境・施設</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>【仮問題26】動画の豚に見られる異常はどれですか？</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>【仮】異常なし</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補B</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補C</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補D</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>【仮】解説26。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>[Placeholder 26] What abnormality is seen in the pig in the video?</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>[TBD] nothing abnormal</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>[TBD] candidate B</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>[TBD] candidate C</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>q27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>videos/dummy-q27.mp4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>肉豚・出荷・肉</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>【仮問題27】動画の場面で、次にすべき行動はどれですか？</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>【仮】行動A</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>【仮】行動B</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>【仮】行動C</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>【仮】行動D</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>【仮】解説27。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>[Placeholder 27] In the situation shown, what should be done next?</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>[TBD] action A</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[TBD] action B</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>[TBD] action C</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>q28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>videos/dummy-q28.mp4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>経営理念・行動規範</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>【仮問題28】動画の場面で、危険なのはどれですか？</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>【仮】危険A</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>【仮】危険B</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>【仮】危険C</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>【仮】危険D</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>【仮】解説28。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>[Placeholder 28] What is dangerous in the situation shown?</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>[TBD] hazard A</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>[TBD] hazard B</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>[TBD] hazard C</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>[TBD] hazard D</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>q29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>videos/dummy-q29.mp4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>繁殖・分娩</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>【仮問題29】動画の作業で、正しくないのはどれですか？</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>【仮】誤っている手順A</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順B</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順C</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>【仮】正しい手順D</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>【仮】解説29。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>[Placeholder 29] Which action in the video is NOT correct?</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>[TBD] wrong step A</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>[TBD] correct step B</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>[TBD] correct step C</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>q30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>videos/dummy-q30.mp4</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>子豚・育成</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>【仮問題30】動画の豚に見られる異常はどれですか？</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>【仮】異常なし</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補B</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補C</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>【仮】異常の候補D</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>【仮】解説30。本物の動画ができたらここに根拠を書く。</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>[Placeholder 30] What abnormality is seen in the pig in the video?</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>[TBD] nothing abnormal</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>[TBD] candidate B</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>[TBD] candidate C</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3486,8 +3327,9 @@
   <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3660,12 +3502,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>videos/dummy-demo01.mp4</t>
+          <t>videos/demo01.mp4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>繁殖・分娩</t>
+          <t>子豚・育成</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3676,27 +3518,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>【仮問題1】動画の作業で、正しくないのはどれですか？</t>
+          <t>動画で子豚の頭に青いスプレーをかけているのはなぜですか？</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>【仮】誤っている手順A</t>
+          <t>処置がすんだ印をつけるため</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順B</t>
+          <t>体をひやすため</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順C</t>
+          <t>虫をよけるため</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>【仮】正しい手順D</t>
+          <t>きれいにするため</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -3704,44 +3546,84 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>【仮】解説1。本物の動画ができたらここに根拠を書く。</t>
+          <t>青いスプレーの印は「処置がすんだ」しるしです。印を見て、まだの豚とすんだ豚を見分けます。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Placeholder 1] Which action in the video is NOT correct?</t>
+          <t>Why is blue spray put on the piglet's head in the video?</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[TBD] wrong step A</t>
+          <t>To mark that the treatment is done</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[TBD] correct step B</t>
+          <t>To cool the body</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[TBD] correct step C</t>
+          <t>To keep insects away</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[TBD] correct step D</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>To clean it</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Vì sao xịt sơn xanh lên đầu heo con trong video?</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Để đánh dấu đã xử lý xong</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Để làm mát cơ thể</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Để đuổi côn trùng</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Để làm sạch</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Mengapa kepala anak babi disemprot biru dalam video?</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Untuk menandai bahwa tindakan sudah selesai</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Untuk mendinginkan badan</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Untuk mengusir serangga</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Untuk membersihkan</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -3756,12 +3638,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>videos/dummy-demo02.mp4</t>
+          <t>videos/demo02.mp4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>子豚・育成</t>
+          <t>肉豚・出荷・肉</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3772,72 +3654,112 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>【仮問題2】動画の豚に見られる異常はどれですか？</t>
+          <t>動画では豚に何をしていますか？</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>【仮】異常なし</t>
+          <t>鼻をワイヤーでおさえて（保定して）、首から血をとっている</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補B</t>
+          <t>鼻に薬をぬっている</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補C</t>
+          <t>口の中を見ている</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>【仮】異常の候補D</t>
+          <t>歯を切っている</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>【仮】解説2。本物の動画ができたらここに根拠を書く。</t>
+          <t>鼻にワイヤーをかけて豚を動かないようにし（鼻保定）、首から注射器で血をとっています（採血）。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Placeholder 2] What abnormality is seen in the pig in the video?</t>
+          <t>What is being done to the pig in the video?</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[TBD] nothing abnormal</t>
+          <t>Holding the snout with a wire snare and taking blood from the neck</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[TBD] candidate B</t>
+          <t>Putting medicine on the snout</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[TBD] candidate C</t>
+          <t>Looking inside the mouth</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[TBD] candidate D</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+          <t>Clipping the teeth</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Trong video đang làm gì với con heo?</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Giữ mũi bằng dây thòng lọng (cố định) và lấy máu ở cổ</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Bôi thuốc lên mũi</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Xem bên trong miệng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Cắt răng</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan pada babi dalam video?</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Menahan hidung dengan jerat kawat dan mengambil darah dari leher</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Mengoles obat di hidung</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Melihat bagian dalam mulut</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Memotong gigi</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -3852,7 +3774,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>videos/dummy-demo03.mp4</t>
+          <t>videos/demo03.mp4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3868,72 +3790,112 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>【仮問題3】動画の場面で、次にすべき行動はどれですか？</t>
+          <t>動画の人は豚舎に入る前に何をしましたか？</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>【仮】行動A</t>
+          <t>豚舎用の長靴にはきかえた</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>【仮】行動B</t>
+          <t>手を消毒した</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>【仮】行動C</t>
+          <t>マスクをつけた</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>【仮】行動D</t>
+          <t>帽子をかぶった</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>【仮】解説3。本物の動画ができたらここに根拠を書く。</t>
+          <t>入口で豚舎用の長靴にはきかえてから中に入っています。外の汚れを持ち込まないためです。</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Placeholder 3] In the situation shown, what should be done next?</t>
+          <t>What did the person do before entering the pig house?</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[TBD] action A</t>
+          <t>Changed into boots for the pig house</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[TBD] action B</t>
+          <t>Disinfected the hands</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[TBD] action C</t>
+          <t>Put on a mask</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[TBD] action D</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+          <t>Put on a hat</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Người trong video đã làm gì trước khi vào chuồng heo?</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Thay sang ủng dành cho chuồng</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Khử trùng tay</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Đeo khẩu trang</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Đội mũ</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan orang itu sebelum masuk kandang?</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Mengganti sepatu bot khusus kandang</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Mendisinfeksi tangan</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Memakai masker</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Memakai topi</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>

--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -3312,6 +3312,1366 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>q21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>videos/q21.mp4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>動画の豚舎はどれですか？</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>母豚と生まれた子豚がいる分娩舎</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>子豚だけの離乳舎</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>出荷前の大きい豚の豚舎</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>えさをためる倉庫</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>分娩柵（母豚が入る柵）のまわりに小さい子豚がいて、子豚用の給餌皿があります。母豚と生まれた子豚がいる分娩舎です。</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Which kind of pig house is shown in the video?</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>A farrowing house with sows and their newborn piglets</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>A nursery with piglets only</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A house for large pigs before shipping</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>A feed storage room</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Chuồng trong video là loại nào?</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Chuồng đẻ có heo mẹ và heo con mới sinh</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Chuồng cai sữa chỉ có heo con</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Chuồng heo lớn trước khi xuất bán</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Kho chứa thức ăn</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kandang jenis apa yang terlihat dalam video?</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Kandang beranak dengan induk dan anak babi baru lahir</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Kandang sapih hanya anak babi</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Kandang babi besar sebelum dijual</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Gudang pakan</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>q22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>videos/q22.mp4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>動画の豚は、どのように飼われていますか？</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1つの豚房に何頭もまとめて入っている</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1頭ずつ柵（ストール）に入っている</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>母豚と子豚がいっしょに入っている</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1頭ずつ外につながれている</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1つの豚房に大きい豚が何頭もまとめて入っています（群飼）。母豚を1頭ずつ入れるストールとはちがいます。</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>How are the pigs in the video kept?</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Several pigs together in one pen</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>One pig per stall</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A sow together with her piglets</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Each pig tied outside</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Heo trong video được nuôi như thế nào?</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Nhiều con chung một ô chuồng</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Mỗi con một ô (chuồng cũi)</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Heo mẹ ở cùng heo con</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Mỗi con buộc riêng ngoài trời</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bagaimana babi dalam video dipelihara?</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Beberapa ekor bersama dalam satu kandang</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Satu ekor per sekat (stall)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Induk bersama anak-anaknya</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Tiap ekor diikat di luar</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>q23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>videos/q23.mp4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>動画では、注射のあとに何をしていますか？</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>注射器を道具のケースにしまっている</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>注射器を床に置いている</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>注射器を豚房に投げている</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>注射器を水につけている</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>使い終わった注射器を道具のケースに戻しています。床や柵の上に置きっぱなしにすると、汚れたり、なくしたり、豚がかんだりします。</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>What is being done after the injection in the video?</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Putting the syringe back into the tool case</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Leaving the syringe on the floor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Throwing the syringe into the pen</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Putting the syringe in water</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Sau khi tiêm, trong video làm gì?</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Cất ống tiêm vào hộp dụng cụ</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Để ống tiêm trên sàn</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ném ống tiêm vào ô chuồng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ngâm ống tiêm vào nước</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan setelah menyuntik dalam video?</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Menyimpan alat suntik ke kotak peralatan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Meletakkan alat suntik di lantai</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Melempar alat suntik ke kandang</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Merendam alat suntik dalam air</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>q24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>videos/q24.mp4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>飼養環境・施設</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>動画の通路で、歩くときに気をつけることは何ですか？</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>床がぬれていてすべりやすいので、足もとを見てゆっくり歩く</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>暗いので走って通る</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>豚がいないので何も気をつけなくてよい</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>柵の上を歩く</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>通路の床がぬれています。ぬれた床はすべりやすく、転んでけがをします。急がず、足もとを見て歩きます。</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>What should you be careful about when walking in the aisle shown?</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>The floor is wet and slippery, so watch your step and walk slowly</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>It is dark, so run through</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>There are no pigs, so nothing to worry about</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Walk on top of the rails</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Khi đi trong lối đi ở video cần chú ý gì?</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Sàn ướt, dễ trượt nên nhìn chân và đi chậm</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Tối nên chạy qua</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Không có heo nên không cần chú ý</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Đi trên thanh chắn</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Apa yang harus diperhatikan saat berjalan di lorong dalam video?</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Lantai basah dan licin, jadi perhatikan langkah dan berjalan pelan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Gelap, jadi lari saja</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Tidak ada babi, jadi tidak perlu hati-hati</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Berjalan di atas pagar</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>q25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>videos/q25.mp4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>動画の人は、いつから防護服を着ていますか？</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>豚舎に入る前、農場の道を歩くときから</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>豚舎の中に入ってから</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>豚にさわる直前だけ</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>着ていない</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>外から来た人は、豚舎に入る前、農場の敷地を歩くときから防護服と長靴を着けています。豚舎の前で着るのではなく、農場に入るときに着ます。</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Since when has the person in the video been wearing the coverall?</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Before entering the pig house, already while walking on the farm road</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Only after entering the pig house</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Only just before touching a pig</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Not wearing one</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Người trong video mặc đồ bảo hộ từ khi nào?</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Từ trước khi vào chuồng, ngay khi đi trên đường trong trại</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Chỉ sau khi vào trong chuồng</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Chỉ ngay trước khi chạm vào heo</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Không mặc</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sejak kapan orang dalam video memakai baju pelindung?</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Sebelum masuk kandang, sudah sejak berjalan di jalan peternakan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Hanya setelah masuk kandang</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Hanya sesaat sebelum menyentuh babi</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Tidak memakai</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>q26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>videos/q26.mp4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>動画の場所は何をする所ですか？</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>使った道具を洗う所</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>豚にえさをやる所</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>薬をしまう所</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>豚を運ぶ所</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>水道と桶、かごがある洗い場です。使った道具をここで洗います。（社長確認: この場所の実際の用途）</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>What is the place in the video used for?</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Washing used tools</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Feeding pigs</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storing medicine</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Loading pigs</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Nơi trong video dùng để làm gì?</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Rửa dụng cụ đã dùng</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Cho heo ăn</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Cất thuốc</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Chuyển heo</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tempat dalam video digunakan untuk apa?</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Mencuci peralatan bekas pakai</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Memberi makan babi</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Menyimpan obat</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Memuat babi</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>q27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>videos/q06.mp4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>動画で、赤いスプレーは子豚のどこにかけていますか？</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>背中</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>しっぽ</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>おなか</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>赤いスプレーは子豚の背中にかけています。背中は上から見えるので、群れの中でも印がすぐ分かります。</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Where on the piglet is the red spray applied in the video?</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>On the back</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>On the legs</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>On the tail</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>On the belly</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Trong video, sơn đỏ được xịt vào đâu trên heo con?</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Lưng</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Chân</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Đuôi</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bụng</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Di bagian mana anak babi disemprot merah dalam video?</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Punggung</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Kaki</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Ekor</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Perut</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>q28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>videos/q12.mp4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>動画のように鼻にワイヤーをかけて保定するのは、どんな豚ですか？</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>手ではおさえられない大きい豚</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>生まれたばかりの子豚</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>死んだ豚</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>寝ている豚</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>動画の豚は大きく、手や体でおさえることができません。だから鼻にワイヤーをかける道具（鼻保定器）で動かないようにします。小さい子豚は手でおさえます。</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Which pigs are restrained with a wire snare on the snout, as in the video?</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Large pigs that cannot be held by hand</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Newborn piglets</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dead pigs</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sleeping pigs</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Loại heo nào được cố định bằng dây thòng lọng ở mũi như trong video?</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Heo lớn không thể giữ bằng tay</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Heo con mới sinh</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Heo đã chết</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Heo đang ngủ</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Babi mana yang ditahan dengan jerat kawat di hidung seperti dalam video?</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Babi besar yang tidak bisa dipegang dengan tangan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Anak babi baru lahir</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Babi mati</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Babi yang tidur</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>q29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>videos/q01.mp4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>動画の人は、長靴の裏を見て何を確認していますか？</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>汚れが残っていないか</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>サイズが合っているか</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>色がきれいか</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>値段</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>長靴の裏（底）を見て、汚れがないか確認しています。長靴の底のみぞには汚れがたまりやすく、病気のもとを運びます。</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>What is the person checking by looking at the sole of the boot?</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Whether any dirt is left</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Whether the size fits</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Whether the color is nice</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>The price</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Người trong video nhìn đế ủng để kiểm tra gì?</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Còn dính bẩn hay không</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Cỡ có vừa không</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Màu có đẹp không</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Giá tiền</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Apa yang diperiksa orang itu dengan melihat sol sepatu bot?</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Apakah masih ada kotoran</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Apakah ukurannya pas</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Apakah warnanya bagus</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Harganya</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>q30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>videos/q13.mp4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>動画でとった豚の血は、何に使いますか？</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>病気の検査</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>豚のえさ</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>肥料</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>捨てる</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>とった血は病気の検査に使います。豚が病気にかかっていないか、ワクチンが効いているかを調べます。</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>What is the blood taken from the pig in the video used for?</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Disease testing</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Pig feed</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fertilizer</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>It is thrown away</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Máu lấy từ heo trong video dùng để làm gì?</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Xét nghiệm bệnh</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Làm thức ăn cho heo</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Làm phân bón</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Vứt bỏ</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Darah yang diambil dari babi dalam video digunakan untuk apa?</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Pemeriksaan penyakit</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Pakan babi</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Pupuk</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Dibuang</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>きれいな場所（事務所）で、薬のびんに針をさして注射器に薬を吸っています。</t>
+          <t>きれいな場所（事務所）で、薬のびんに針をさして注射器に薬を吸っています。ほこりや汚れの少ない場所で準備します。</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>水道と桶、かごがある洗い場です。使った道具をここで洗います。（社長確認: この場所の実際の用途）</t>
+          <t>水道と桶、かごがある洗い場です。使った道具をここで洗います。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
